--- a/history_prices/APR/prices_04042026.xlsx
+++ b/history_prices/APR/prices_04042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\history_prices\APR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DBAD837-7969-4522-AE3D-25F8810C49CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D84FB1-DB6A-4CA2-B093-9EF8E6D1E0AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="178">
   <si>
     <t>ID</t>
   </si>
@@ -542,6 +542,18 @@
   </si>
   <si>
     <t>ОТСТЪПКА</t>
+  </si>
+  <si>
+    <t>0201</t>
+  </si>
+  <si>
+    <t>0202</t>
+  </si>
+  <si>
+    <t>АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ</t>
+  </si>
+  <si>
+    <t>000455464</t>
   </si>
 </sst>
 </file>
@@ -549,14 +561,20 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="&quot;€&quot;#,##0.000_-"/>
-    <numFmt numFmtId="167" formatCode="&quot;€&quot;#,##0.00_-"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="&quot;€&quot;#,##0.000_-"/>
+    <numFmt numFmtId="166" formatCode="&quot;€&quot;#,##0.00_-"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -582,12 +600,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -890,18 +909,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="23.28515625" customWidth="1"/>
+    <col min="3" max="3" width="59.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="26.42578125" customWidth="1"/>
     <col min="6" max="6" width="23.28515625" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="28.140625" customWidth="1"/>
     <col min="9" max="9" width="27.42578125" customWidth="1"/>
-    <col min="10" max="13" width="23.28515625" customWidth="1"/>
+    <col min="10" max="12" width="23.28515625" customWidth="1"/>
+    <col min="13" max="13" width="23.28515625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -941,7 +961,7 @@
       <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -976,7 +996,7 @@
       <c r="J2" t="s">
         <v>16</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1011,7 +1031,7 @@
       <c r="J3" t="s">
         <v>16</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1046,7 +1066,7 @@
       <c r="J4" t="s">
         <v>22</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1081,7 +1101,7 @@
       <c r="J5" t="s">
         <v>22</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1119,7 +1139,7 @@
       <c r="K6" t="s">
         <v>28</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M6" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1157,7 +1177,7 @@
       <c r="K7" t="s">
         <v>28</v>
       </c>
-      <c r="M7" t="s">
+      <c r="M7" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1192,7 +1212,7 @@
       <c r="J8" t="s">
         <v>33</v>
       </c>
-      <c r="M8" t="s">
+      <c r="M8" s="5" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1227,7 +1247,7 @@
       <c r="J9" t="s">
         <v>33</v>
       </c>
-      <c r="M9" t="s">
+      <c r="M9" s="5" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1262,7 +1282,7 @@
       <c r="J10" t="s">
         <v>38</v>
       </c>
-      <c r="M10" t="s">
+      <c r="M10" s="5" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1303,7 +1323,7 @@
       <c r="L11" t="s">
         <v>44</v>
       </c>
-      <c r="M11" t="s">
+      <c r="M11" s="5" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1344,7 +1364,7 @@
       <c r="L12" t="s">
         <v>44</v>
       </c>
-      <c r="M12" t="s">
+      <c r="M12" s="5" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1379,7 +1399,7 @@
       <c r="J13" t="s">
         <v>49</v>
       </c>
-      <c r="M13" t="s">
+      <c r="M13" s="5" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1414,7 +1434,7 @@
       <c r="J14" t="s">
         <v>49</v>
       </c>
-      <c r="M14" t="s">
+      <c r="M14" s="5" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1449,7 +1469,7 @@
       <c r="J15" t="s">
         <v>54</v>
       </c>
-      <c r="M15" t="s">
+      <c r="M15" s="5" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1484,7 +1504,7 @@
       <c r="J16" t="s">
         <v>54</v>
       </c>
-      <c r="M16" t="s">
+      <c r="M16" s="5" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1519,7 +1539,7 @@
       <c r="J17" t="s">
         <v>59</v>
       </c>
-      <c r="M17" t="s">
+      <c r="M17" s="5" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1554,7 +1574,7 @@
       <c r="J18" t="s">
         <v>59</v>
       </c>
-      <c r="M18" t="s">
+      <c r="M18" s="5" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1592,7 +1612,7 @@
       <c r="K19" t="s">
         <v>65</v>
       </c>
-      <c r="M19" t="s">
+      <c r="M19" s="5" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1630,7 +1650,7 @@
       <c r="K20" t="s">
         <v>65</v>
       </c>
-      <c r="M20" t="s">
+      <c r="M20" s="5" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1668,7 +1688,7 @@
       <c r="K21" t="s">
         <v>65</v>
       </c>
-      <c r="M21" t="s">
+      <c r="M21" s="5" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1706,7 +1726,7 @@
       <c r="K22" t="s">
         <v>65</v>
       </c>
-      <c r="M22" t="s">
+      <c r="M22" s="5" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1744,7 +1764,7 @@
       <c r="K23" t="s">
         <v>75</v>
       </c>
-      <c r="M23" t="s">
+      <c r="M23" s="5" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1782,7 +1802,7 @@
       <c r="K24" t="s">
         <v>75</v>
       </c>
-      <c r="M24" t="s">
+      <c r="M24" s="5" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1820,7 +1840,7 @@
       <c r="K25" t="s">
         <v>75</v>
       </c>
-      <c r="M25" t="s">
+      <c r="M25" s="5" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1858,7 +1878,7 @@
       <c r="K26" t="s">
         <v>75</v>
       </c>
-      <c r="M26" t="s">
+      <c r="M26" s="5" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1893,7 +1913,7 @@
       <c r="J27" t="s">
         <v>82</v>
       </c>
-      <c r="M27" t="s">
+      <c r="M27" s="5" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1928,7 +1948,7 @@
       <c r="J28" t="s">
         <v>82</v>
       </c>
-      <c r="M28" t="s">
+      <c r="M28" s="5" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1966,7 +1986,7 @@
       <c r="K29" t="s">
         <v>88</v>
       </c>
-      <c r="M29" t="s">
+      <c r="M29" s="5" t="s">
         <v>89</v>
       </c>
     </row>
@@ -2004,7 +2024,7 @@
       <c r="K30" t="s">
         <v>88</v>
       </c>
-      <c r="M30" t="s">
+      <c r="M30" s="5" t="s">
         <v>89</v>
       </c>
     </row>
@@ -2039,7 +2059,7 @@
       <c r="J31" t="s">
         <v>93</v>
       </c>
-      <c r="M31" t="s">
+      <c r="M31" s="5" t="s">
         <v>94</v>
       </c>
     </row>
@@ -2074,7 +2094,7 @@
       <c r="J32" t="s">
         <v>93</v>
       </c>
-      <c r="M32" t="s">
+      <c r="M32" s="5" t="s">
         <v>94</v>
       </c>
     </row>
@@ -2109,7 +2129,7 @@
       <c r="J33" t="s">
         <v>98</v>
       </c>
-      <c r="M33" t="s">
+      <c r="M33" s="5" t="s">
         <v>99</v>
       </c>
     </row>
@@ -2147,7 +2167,7 @@
       <c r="K34" t="s">
         <v>103</v>
       </c>
-      <c r="M34" t="s">
+      <c r="M34" s="5" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2185,7 +2205,7 @@
       <c r="K35" t="s">
         <v>103</v>
       </c>
-      <c r="M35" t="s">
+      <c r="M35" s="5" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2220,7 +2240,7 @@
       <c r="J36" t="s">
         <v>108</v>
       </c>
-      <c r="M36" t="s">
+      <c r="M36" s="5" t="s">
         <v>109</v>
       </c>
     </row>
@@ -2255,7 +2275,7 @@
       <c r="J37" t="s">
         <v>112</v>
       </c>
-      <c r="M37" t="s">
+      <c r="M37" s="5" t="s">
         <v>113</v>
       </c>
     </row>
@@ -2290,7 +2310,7 @@
       <c r="J38" t="s">
         <v>112</v>
       </c>
-      <c r="M38" t="s">
+      <c r="M38" s="5" t="s">
         <v>113</v>
       </c>
     </row>
@@ -2328,7 +2348,7 @@
       <c r="K39" t="s">
         <v>118</v>
       </c>
-      <c r="M39" t="s">
+      <c r="M39" s="5" t="s">
         <v>119</v>
       </c>
     </row>
@@ -2366,7 +2386,7 @@
       <c r="K40" t="s">
         <v>118</v>
       </c>
-      <c r="M40" t="s">
+      <c r="M40" s="5" t="s">
         <v>119</v>
       </c>
     </row>
@@ -2404,7 +2424,7 @@
       <c r="K41" t="s">
         <v>118</v>
       </c>
-      <c r="M41" t="s">
+      <c r="M41" s="5" t="s">
         <v>119</v>
       </c>
     </row>
@@ -2442,7 +2462,7 @@
       <c r="K42" t="s">
         <v>118</v>
       </c>
-      <c r="M42" t="s">
+      <c r="M42" s="5" t="s">
         <v>119</v>
       </c>
     </row>
@@ -2477,7 +2497,7 @@
       <c r="J43" t="s">
         <v>125</v>
       </c>
-      <c r="M43" t="s">
+      <c r="M43" s="5" t="s">
         <v>126</v>
       </c>
     </row>
@@ -2512,7 +2532,7 @@
       <c r="J44" t="s">
         <v>125</v>
       </c>
-      <c r="M44" t="s">
+      <c r="M44" s="5" t="s">
         <v>126</v>
       </c>
     </row>
@@ -2550,7 +2570,7 @@
       <c r="K45" t="s">
         <v>131</v>
       </c>
-      <c r="M45" t="s">
+      <c r="M45" s="5" t="s">
         <v>132</v>
       </c>
     </row>
@@ -2588,7 +2608,7 @@
       <c r="K46" t="s">
         <v>131</v>
       </c>
-      <c r="M46" t="s">
+      <c r="M46" s="5" t="s">
         <v>132</v>
       </c>
     </row>
@@ -2626,7 +2646,7 @@
       <c r="K47" t="s">
         <v>131</v>
       </c>
-      <c r="M47" t="s">
+      <c r="M47" s="5" t="s">
         <v>132</v>
       </c>
     </row>
@@ -2664,7 +2684,7 @@
       <c r="K48" t="s">
         <v>131</v>
       </c>
-      <c r="M48" t="s">
+      <c r="M48" s="5" t="s">
         <v>132</v>
       </c>
     </row>
@@ -2702,7 +2722,7 @@
       <c r="K49" t="s">
         <v>139</v>
       </c>
-      <c r="M49" t="s">
+      <c r="M49" s="5" t="s">
         <v>140</v>
       </c>
     </row>
@@ -2740,7 +2760,7 @@
       <c r="K50" t="s">
         <v>139</v>
       </c>
-      <c r="M50" t="s">
+      <c r="M50" s="5" t="s">
         <v>140</v>
       </c>
     </row>
@@ -2778,7 +2798,7 @@
       <c r="K51" t="s">
         <v>139</v>
       </c>
-      <c r="M51" t="s">
+      <c r="M51" s="5" t="s">
         <v>140</v>
       </c>
     </row>
@@ -2816,7 +2836,7 @@
       <c r="K52" t="s">
         <v>139</v>
       </c>
-      <c r="M52" t="s">
+      <c r="M52" s="5" t="s">
         <v>140</v>
       </c>
     </row>
@@ -2845,7 +2865,7 @@
       <c r="H53" s="3">
         <v>1.6879999999999999</v>
       </c>
-      <c r="M53" t="s">
+      <c r="M53" s="5" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2874,7 +2894,7 @@
       <c r="H54" s="3">
         <v>1.6879999999999999</v>
       </c>
-      <c r="M54" t="s">
+      <c r="M54" s="5" t="s">
         <v>149</v>
       </c>
     </row>
@@ -2903,7 +2923,7 @@
       <c r="H55" s="3">
         <v>1.6879999999999999</v>
       </c>
-      <c r="M55" t="s">
+      <c r="M55" s="5" t="s">
         <v>152</v>
       </c>
     </row>
@@ -2932,7 +2952,7 @@
       <c r="H56" s="3">
         <v>1.6879999999999999</v>
       </c>
-      <c r="M56" t="s">
+      <c r="M56" s="5" t="s">
         <v>155</v>
       </c>
     </row>
@@ -2961,7 +2981,7 @@
       <c r="H57" s="3">
         <v>1.6879999999999999</v>
       </c>
-      <c r="M57" t="s">
+      <c r="M57" s="5" t="s">
         <v>158</v>
       </c>
     </row>
@@ -2990,7 +3010,7 @@
       <c r="H58" s="3">
         <v>1.4390000000000001</v>
       </c>
-      <c r="M58" t="s">
+      <c r="M58" s="5" t="s">
         <v>152</v>
       </c>
     </row>
@@ -3019,7 +3039,7 @@
       <c r="H59" s="3">
         <v>1.429</v>
       </c>
-      <c r="M59" t="s">
+      <c r="M59" s="5" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3048,7 +3068,7 @@
       <c r="H60" s="3">
         <v>1.6879999999999999</v>
       </c>
-      <c r="M60" t="s">
+      <c r="M60" s="5" t="s">
         <v>163</v>
       </c>
     </row>
@@ -3077,7 +3097,7 @@
       <c r="H61" s="3">
         <v>1.429</v>
       </c>
-      <c r="M61" t="s">
+      <c r="M61" s="5" t="s">
         <v>163</v>
       </c>
     </row>
@@ -3106,7 +3126,7 @@
       <c r="H62" s="3">
         <v>1.419</v>
       </c>
-      <c r="M62" t="s">
+      <c r="M62" s="5" t="s">
         <v>158</v>
       </c>
     </row>
@@ -3135,7 +3155,7 @@
       <c r="H63" s="3">
         <v>1.419</v>
       </c>
-      <c r="M63" t="s">
+      <c r="M63" s="5" t="s">
         <v>155</v>
       </c>
     </row>
@@ -3164,7 +3184,7 @@
       <c r="H64" s="3">
         <v>1.429</v>
       </c>
-      <c r="M64" t="s">
+      <c r="M64" s="5" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3199,7 +3219,7 @@
       <c r="J65" t="s">
         <v>170</v>
       </c>
-      <c r="M65" t="s">
+      <c r="M65" s="5" t="s">
         <v>171</v>
       </c>
     </row>
@@ -3234,11 +3254,70 @@
       <c r="J66" t="s">
         <v>170</v>
       </c>
-      <c r="M66" t="s">
+      <c r="M66" s="5" t="s">
         <v>171</v>
       </c>
     </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>174</v>
+      </c>
+      <c r="B67" s="1">
+        <v>46116</v>
+      </c>
+      <c r="C67" t="s">
+        <v>176</v>
+      </c>
+      <c r="D67" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="4">
+        <v>0.04</v>
+      </c>
+      <c r="F67" s="2">
+        <v>1.6779999999999999</v>
+      </c>
+      <c r="G67" s="2">
+        <v>0</v>
+      </c>
+      <c r="H67" s="2">
+        <v>1.6779999999999999</v>
+      </c>
+      <c r="M67" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>175</v>
+      </c>
+      <c r="B68" s="1">
+        <v>46116</v>
+      </c>
+      <c r="C68" t="s">
+        <v>176</v>
+      </c>
+      <c r="D68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E68" s="4">
+        <v>0.04</v>
+      </c>
+      <c r="F68" s="2">
+        <v>1.399</v>
+      </c>
+      <c r="G68" s="2">
+        <v>0</v>
+      </c>
+      <c r="H68" s="2">
+        <v>1.399</v>
+      </c>
+      <c r="M68" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>